--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6 â€” 147</t>
+          <t>L10: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 69â€”70</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]167</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]167</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 7.</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L6: isolated marker/symbol line :: /</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]167</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -628,7 +632,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • the English Orders</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,12 +668,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 70â€”71</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • the English Orders</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -677,13 +685,17 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L18: isolated marker/symbol line :: 0</t>
+          <t>L6: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 71 to 74</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -715,12 +727,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | symbol-only separator/garbage line :: ： 66</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ the English Orders</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -732,13 +744,17 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L22: symbol-only separator/garbage line :: , 112</t>
+          <t>L18: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 13 to 13</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -754,12 +770,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -770,12 +786,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 70 â€” 71</t>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 71 to 74</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -787,13 +803,17 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L24: isolated marker/symbol line :: 115</t>
+          <t>L22: symbol-only separator/garbage line :: , 112</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L157: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: •65</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -825,12 +845,12 @@
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To appear and answerâ€”form of</t>
+          <t>L109: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6â€”147</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 13 to 13</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -842,7 +862,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L26: symbol-only separator/garbage line :: . 116</t>
+          <t>L24: isolated marker/symbol line :: 115</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -880,24 +900,24 @@
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 65 â€” 66</t>
+          <t>L119: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 71 to 74</t>
+          <t>L142: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L9: symbol-only separator/garbage line :: 6 — 147</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: 70</t>
+          <t>L26: symbol-only separator/garbage line :: . 116</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -933,26 +953,22 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 49â€”50</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 26</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L10: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: 71</t>
+          <t>L30: symbol-only separator/garbage line :: . 69—70</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -988,26 +1004,22 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Mode of service of Subp Ã¦ ena</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 13 to 13</t>
+          <t>L151: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: 167</t>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L52: symbol-only separator/garbage line :: 7. 13</t>
+          <t>L32: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1029,12 +1041,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1043,26 +1055,22 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ na to amended Bill, m</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L116: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SUBPÅ’NA.â€”WRIT OF</t>
+          <t>L153: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 112</t>
+          <t>L25: isolated marker/symbol line :: 167</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: 13</t>
+          <t>L34: symbol-only separator/garbage line :: . 70—71</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1089,7 +1097,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1098,26 +1106,22 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Form of Subp Ã¦ na to amended</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To appear and answerâ€”form of</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L28: isolated marker/symbol line :: 115</t>
+          <t>L27: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: e</t>
+          <t>L36: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1139,12 +1143,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1153,26 +1157,22 @@
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: ice of SubpÃ¦na. .</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L157: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: •65</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L31: symbol-only separator/garbage line :: 69-70</t>
+          <t>L28: isolated marker/symbol line :: 115</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L70: symbol-only separator/garbage line :: .15</t>
+          <t>L52: symbol-only separator/garbage line :: 7. 13</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1208,26 +1208,22 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 26 â€” 27</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ . 26</t>
+          <t>L177: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: 70</t>
+          <t>L31: symbol-only separator/garbage line :: 69-70</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L74: symbol-only separator/garbage line :: . 110</t>
+          <t>L54: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1254,7 +1250,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1263,26 +1259,18 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L113: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: p Ã¦ ena to amended Bill</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 26â€”27</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 71</t>
+          <t>L32: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L80: symbol-only separator/garbage line :: .73</t>
+          <t>L58: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1318,26 +1306,18 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 48</t>
+          <t>L34: symbol-only separator/garbage line :: 70 — 71</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L82: symbol-only separator/garbage line :: .48</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1374,21 +1354,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 48</t>
+          <t>L35: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 48</t>
+          <t>L70: symbol-only separator/garbage line :: .15</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1425,21 +1401,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 49</t>
+          <t>L38: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L86: symbol-only separator/garbage line :: .49</t>
+          <t>L74: symbol-only separator/garbage line :: . 110</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1464,21 +1436,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L157: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢65</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 49</t>
+          <t>L39: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 49</t>
+          <t>L75: symbol-only separator/garbage line :: 6—147</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1503,21 +1471,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L161: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 65â€”66</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L42: symbol-only separator/garbage line :: 49-50</t>
+          <t>L40: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 49</t>
+          <t>L80: symbol-only separator/garbage line :: .73</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1542,21 +1506,17 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 49</t>
+          <t>L41: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L94: symbol-only separator/garbage line :: .50</t>
+          <t>L82: symbol-only separator/garbage line :: .48</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1586,12 +1546,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 50</t>
+          <t>L42: symbol-only separator/garbage line :: 49-50</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 50</t>
+          <t>L84: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1621,12 +1581,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L45: symbol-only separator/garbage line :: 50.</t>
+          <t>L43: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 3</t>
+          <t>L86: symbol-only separator/garbage line :: .49</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1656,12 +1616,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 109</t>
+          <t>L44: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L136: symbol-only separator/garbage line :: . 109</t>
+          <t>L88: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1691,12 +1651,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 111</t>
+          <t>L45: symbol-only separator/garbage line :: 50.</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: 111</t>
+          <t>L90: symbol-only separator/garbage line :: 49—50</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1726,12 +1686,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: '</t>
+          <t>L46: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 65</t>
+          <t>L92: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1761,12 +1721,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 7</t>
+          <t>L47: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L94: symbol-only separator/garbage line :: .50</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1796,12 +1756,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: '</t>
+          <t>L52: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L144: symbol-only separator/garbage line :: . 25</t>
+          <t>L96: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1831,12 +1791,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: e</t>
+          <t>L53: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 26</t>
+          <t>L98: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1866,12 +1826,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 73</t>
+          <t>L54: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L136: symbol-only separator/garbage line :: . 109</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1901,12 +1861,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 3</t>
+          <t>L65: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L137: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1936,12 +1896,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L77: symbol-only separator/garbage line :: . 25</t>
+          <t>L69: isolated marker/symbol line :: 73</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L140: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1971,12 +1931,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 26</t>
+          <t>L71: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L159: isolated marker/symbol line :: 65</t>
+          <t>L142: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2006,12 +1966,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 65</t>
+          <t>L77: symbol-only separator/garbage line :: . 25</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L163: isolated marker/symbol line :: 66</t>
+          <t>L144: symbol-only separator/garbage line :: . 25</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2041,12 +2001,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 65</t>
+          <t>L78: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L165: symbol-only separator/garbage line :: .66</t>
+          <t>L146: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2076,12 +2036,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 65</t>
+          <t>L80: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L167: isolated marker/symbol line :: *</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 26</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2111,12 +2071,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 66</t>
+          <t>L81: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L169: isolated marker/symbol line :: 67</t>
+          <t>L149: symbol-only separator/garbage line :: 26—27</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2146,12 +2106,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L82: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L171: symbol-only separator/garbage line :: . 108</t>
+          <t>L151: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2181,12 +2141,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: 67</t>
+          <t>L83: symbol-only separator/garbage line :: 65 — 66</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L153: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2216,12 +2176,12 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 108</t>
+          <t>L84: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L179: isolated marker/symbol line :: ,</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2251,12 +2211,12 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 7</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | symbol-only separator/garbage line :: ： 66</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L181: isolated marker/symbol line :: a</t>
+          <t>L157: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: •65</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2286,10 +2246,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L101: symbol-only separator/garbage line :: . 26</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L159: isolated marker/symbol line :: 65</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2317,10 +2281,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 0</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L87: isolated marker/symbol line :: 67</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L161: symbol-only separator/garbage line :: 65—66</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2348,10 +2316,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: .</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L88: isolated marker/symbol line :: 108</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L163: isolated marker/symbol line :: 66</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2379,10 +2351,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: 27</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L99: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L165: symbol-only separator/garbage line :: .66</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2410,10 +2386,14 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: 28</t>
-        </is>
-      </c>
-      <c r="O45" s="1" t="inlineStr"/>
+          <t>L101: symbol-only separator/garbage line :: . 26</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>L167: isolated marker/symbol line :: *</t>
+        </is>
+      </c>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr"/>
       <c r="R45" s="1" t="inlineStr"/>
@@ -2441,10 +2421,14 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L114: isolated marker/symbol line :: 28</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr"/>
+          <t>L103: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>L169: isolated marker/symbol line :: 67</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
       <c r="R46" s="1" t="inlineStr"/>
@@ -2472,10 +2456,14 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 29</t>
-        </is>
-      </c>
-      <c r="O47" s="1" t="inlineStr"/>
+          <t>L104: symbol-only separator/garbage line :: 26 — 27</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L171: symbol-only separator/garbage line :: . 108</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -2503,10 +2491,14 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="O48" s="1" t="inlineStr"/>
+          <t>L108: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>L177: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr"/>
       <c r="R48" s="1" t="inlineStr"/>
@@ -2518,6 +2510,200 @@
       <c r="X48" s="1" t="inlineStr"/>
       <c r="Y48" s="1" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr"/>
+      <c r="B49" s="1" t="inlineStr"/>
+      <c r="C49" s="1" t="inlineStr"/>
+      <c r="D49" s="1" t="inlineStr"/>
+      <c r="E49" s="1" t="inlineStr"/>
+      <c r="F49" s="1" t="inlineStr"/>
+      <c r="G49" s="1" t="inlineStr"/>
+      <c r="H49" s="1" t="inlineStr"/>
+      <c r="I49" s="1" t="inlineStr"/>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
+      <c r="L49" s="1" t="inlineStr"/>
+      <c r="M49" s="1" t="inlineStr"/>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>L109: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>L179: isolated marker/symbol line :: ,</t>
+        </is>
+      </c>
+      <c r="P49" s="1" t="inlineStr"/>
+      <c r="Q49" s="1" t="inlineStr"/>
+      <c r="R49" s="1" t="inlineStr"/>
+      <c r="S49" s="1" t="inlineStr"/>
+      <c r="T49" s="1" t="inlineStr"/>
+      <c r="U49" s="1" t="inlineStr"/>
+      <c r="V49" s="1" t="inlineStr"/>
+      <c r="W49" s="1" t="inlineStr"/>
+      <c r="X49" s="1" t="inlineStr"/>
+      <c r="Y49" s="1" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr"/>
+      <c r="B50" s="1" t="inlineStr"/>
+      <c r="C50" s="1" t="inlineStr"/>
+      <c r="D50" s="1" t="inlineStr"/>
+      <c r="E50" s="1" t="inlineStr"/>
+      <c r="F50" s="1" t="inlineStr"/>
+      <c r="G50" s="1" t="inlineStr"/>
+      <c r="H50" s="1" t="inlineStr"/>
+      <c r="I50" s="1" t="inlineStr"/>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
+      <c r="L50" s="1" t="inlineStr"/>
+      <c r="M50" s="1" t="inlineStr"/>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>L110: isolated marker/symbol line :: 27</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>L181: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
+      <c r="P50" s="1" t="inlineStr"/>
+      <c r="Q50" s="1" t="inlineStr"/>
+      <c r="R50" s="1" t="inlineStr"/>
+      <c r="S50" s="1" t="inlineStr"/>
+      <c r="T50" s="1" t="inlineStr"/>
+      <c r="U50" s="1" t="inlineStr"/>
+      <c r="V50" s="1" t="inlineStr"/>
+      <c r="W50" s="1" t="inlineStr"/>
+      <c r="X50" s="1" t="inlineStr"/>
+      <c r="Y50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="1" t="inlineStr"/>
+      <c r="C51" s="1" t="inlineStr"/>
+      <c r="D51" s="1" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr"/>
+      <c r="G51" s="1" t="inlineStr"/>
+      <c r="H51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr"/>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
+      <c r="L51" s="1" t="inlineStr"/>
+      <c r="M51" s="1" t="inlineStr"/>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>L112: isolated marker/symbol line :: 28</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr"/>
+      <c r="P51" s="1" t="inlineStr"/>
+      <c r="Q51" s="1" t="inlineStr"/>
+      <c r="R51" s="1" t="inlineStr"/>
+      <c r="S51" s="1" t="inlineStr"/>
+      <c r="T51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="inlineStr"/>
+      <c r="V51" s="1" t="inlineStr"/>
+      <c r="W51" s="1" t="inlineStr"/>
+      <c r="X51" s="1" t="inlineStr"/>
+      <c r="Y51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>L114: isolated marker/symbol line :: 28</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+      <c r="W52" s="1" t="inlineStr"/>
+      <c r="X52" s="1" t="inlineStr"/>
+      <c r="Y52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="1" t="inlineStr"/>
+      <c r="C53" s="1" t="inlineStr"/>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr"/>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr"/>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
+      <c r="L53" s="1" t="inlineStr"/>
+      <c r="M53" s="1" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>L116: isolated marker/symbol line :: 29</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr"/>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr"/>
+      <c r="S53" s="1" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr"/>
+      <c r="V53" s="1" t="inlineStr"/>
+      <c r="W53" s="1" t="inlineStr"/>
+      <c r="X53" s="1" t="inlineStr"/>
+      <c r="Y53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr"/>
+      <c r="B54" s="1" t="inlineStr"/>
+      <c r="C54" s="1" t="inlineStr"/>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr"/>
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr"/>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
+      <c r="L54" s="1" t="inlineStr"/>
+      <c r="M54" s="1" t="inlineStr"/>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>L119: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr"/>
+      <c r="P54" s="1" t="inlineStr"/>
+      <c r="Q54" s="1" t="inlineStr"/>
+      <c r="R54" s="1" t="inlineStr"/>
+      <c r="S54" s="1" t="inlineStr"/>
+      <c r="T54" s="1" t="inlineStr"/>
+      <c r="U54" s="1" t="inlineStr"/>
+      <c r="V54" s="1" t="inlineStr"/>
+      <c r="W54" s="1" t="inlineStr"/>
+      <c r="X54" s="1" t="inlineStr"/>
+      <c r="Y54" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
